--- a/public/downloads/BaseraImplications2025.xlsx
+++ b/public/downloads/BaseraImplications2025.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="56">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>O</t>
@@ -662,10 +685,10 @@
         <v>150</v>
       </c>
       <c r="N3" s="5">
-        <v>774.9204216003418</v>
+        <v>774920.4216003418</v>
       </c>
       <c r="O3" s="4">
-        <v>0.0319475767480352</v>
+        <v>31.9475767480352</v>
       </c>
       <c r="P3" s="5">
         <v>24256</v>
@@ -712,10 +735,10 @@
         <v>150</v>
       </c>
       <c r="N4" s="5">
-        <v>1432.82838010788</v>
+        <v>1432828.38010788</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04968542825812746</v>
+        <v>49.68542825812746</v>
       </c>
       <c r="P4" s="5">
         <v>28838</v>
@@ -762,10 +785,10 @@
         <v>150</v>
       </c>
       <c r="N5" s="5">
-        <v>3327.495409250259</v>
+        <v>3327495.409250259</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1324481713668853</v>
+        <v>132.4481713668853</v>
       </c>
       <c r="P5" s="5">
         <v>25123</v>
@@ -812,10 +835,10 @@
         <v>150</v>
       </c>
       <c r="N6" s="5">
-        <v>2055.755521774292</v>
+        <v>2055755.521774292</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08539318442196112</v>
+        <v>85.39318442196111</v>
       </c>
       <c r="P6" s="5">
         <v>24074</v>
@@ -862,10 +885,10 @@
         <v>150</v>
       </c>
       <c r="N7" s="5">
-        <v>4855.341718435287</v>
+        <v>4855341.718435287</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2055258092801933</v>
+        <v>205.5258092801934</v>
       </c>
       <c r="P7" s="5">
         <v>23624</v>
@@ -912,10 +935,10 @@
         <v>150</v>
       </c>
       <c r="N8" s="5">
-        <v>371.415370464325</v>
+        <v>371415.370464325</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01393940215666447</v>
+        <v>13.93940215666447</v>
       </c>
       <c r="P8" s="5">
         <v>26645</v>
@@ -962,10 +985,10 @@
         <v>150</v>
       </c>
       <c r="N9" s="5">
-        <v>711.9259693622589</v>
+        <v>711925.9693622589</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02803299611601271</v>
+        <v>28.03299611601271</v>
       </c>
       <c r="P9" s="5">
         <v>25396</v>
@@ -1012,10 +1035,10 @@
         <v>150</v>
       </c>
       <c r="N10" s="5">
-        <v>2150.7077729702</v>
+        <v>2150707.7729702</v>
       </c>
       <c r="O10" s="4">
-        <v>0.0869043063265799</v>
+        <v>86.9043063265799</v>
       </c>
       <c r="P10" s="5">
         <v>24748</v>
@@ -1062,10 +1085,10 @@
         <v>150</v>
       </c>
       <c r="N11" s="5">
-        <v>1199.898225307465</v>
+        <v>1199898.225307465</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04345567960696308</v>
+        <v>43.45567960696308</v>
       </c>
       <c r="P11" s="5">
         <v>27612</v>
@@ -1112,10 +1135,10 @@
         <v>150</v>
       </c>
       <c r="N12" s="5">
-        <v>443.2937927246094</v>
+        <v>443293.7927246094</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02290923993408834</v>
+        <v>22.90923993408834</v>
       </c>
       <c r="P12" s="5">
         <v>19350</v>
@@ -1162,10 +1185,10 @@
         <v>150</v>
       </c>
       <c r="N13" s="5">
-        <v>2045.763631820679</v>
+        <v>2045763.631820679</v>
       </c>
       <c r="O13" s="4">
-        <v>0.08119398443485787</v>
+        <v>81.19398443485787</v>
       </c>
       <c r="P13" s="5">
         <v>25196</v>
@@ -1212,10 +1235,10 @@
         <v>150</v>
       </c>
       <c r="N14" s="5">
-        <v>14011.77394533157</v>
+        <v>14011773.94533157</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2862057304436868</v>
+        <v>286.2057304436868</v>
       </c>
       <c r="P14" s="5">
         <v>48957</v>
@@ -1262,10 +1285,10 @@
         <v>150</v>
       </c>
       <c r="N15" s="5">
-        <v>4222.422600746155</v>
+        <v>4222422.600746155</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2992927842887833</v>
+        <v>299.2927842887833</v>
       </c>
       <c r="P15" s="5">
         <v>14108</v>
@@ -1312,10 +1335,10 @@
         <v>150</v>
       </c>
       <c r="N16" s="5">
-        <v>4302.101472139359</v>
+        <v>4302101.472139359</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09559588187763834</v>
+        <v>95.59588187763835</v>
       </c>
       <c r="P16" s="5">
         <v>45003</v>
@@ -1362,10 +1385,10 @@
         <v>150</v>
       </c>
       <c r="N17" s="5">
-        <v>1478.746902227402</v>
+        <v>1478746.902227402</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1023283442133694</v>
+        <v>102.3283442133694</v>
       </c>
       <c r="P17" s="5">
         <v>14451</v>
@@ -1393,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1404,9 +1427,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1440,8 +1469,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1463,25 +1500,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3326681399481179</v>
+        <v>0.3636715244984057</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1574533365298825</v>
+        <v>0.2519631518539493</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2000317807008546</v>
+        <v>0.261643783559553</v>
       </c>
       <c r="E3" s="4">
-        <v>89.41807157645688</v>
+        <v>86.73580301685841</v>
       </c>
       <c r="F3" s="4">
-        <v>89.32727847485678</v>
+        <v>86.30823849820034</v>
       </c>
       <c r="G3" s="5">
         <v>92</v>
@@ -1490,80 +1545,116 @@
         <v>75</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.009089151870302483</v>
+      </c>
+      <c r="O3" s="5">
+        <v>75</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3636715244984057</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2511148310127211</v>
+      </c>
+      <c r="R3" s="5">
+        <v>75</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1901769153499109</v>
+        <v>0.3292234900078352</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1719733632622261</v>
+        <v>0.25888597643543</v>
       </c>
       <c r="D4" s="4">
-        <v>0.172103677998634</v>
+        <v>0.2810787510715506</v>
       </c>
       <c r="E4" s="4">
-        <v>90.41339612768152</v>
+        <v>86.09301412872787</v>
       </c>
       <c r="F4" s="4">
-        <v>91.19880399242926</v>
+        <v>85.78729994837293</v>
       </c>
       <c r="G4" s="5">
         <v>52</v>
       </c>
       <c r="H4" s="5">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.06884394429046693</v>
+      </c>
+      <c r="O4" s="5">
+        <v>44</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3263133053419577</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2648344778699112</v>
+      </c>
+      <c r="R4" s="5">
+        <v>44</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6649969520836905</v>
+        <v>0.6600468034638093</v>
       </c>
       <c r="C5" s="4">
-        <v>0.8451054879623889</v>
+        <v>0.100376485632296</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5481892231199433</v>
+        <v>0.5639214192819656</v>
       </c>
       <c r="E5" s="4">
-        <v>85.40816326530617</v>
+        <v>81.4965986394558</v>
       </c>
       <c r="F5" s="4">
-        <v>82.95302013422808</v>
+        <v>71.67785234899375</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
@@ -1572,39 +1663,55 @@
         <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6600468034638093</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.100376485632296</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2180256017020499</v>
+        <v>0.2028008593134955</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2717138494836493</v>
+        <v>0.2770928691424031</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1587259276972919</v>
+        <v>0.2888188735862229</v>
       </c>
       <c r="E6" s="4">
-        <v>89.30839002267574</v>
+        <v>88.70748299319729</v>
       </c>
       <c r="F6" s="4">
-        <v>79.61595824011961</v>
+        <v>80.32438478747228</v>
       </c>
       <c r="G6" s="5">
         <v>3</v>
@@ -1627,9 +1734,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2028008593134955</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2770928691424031</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1640,6 +1763,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1647,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1658,9 +1782,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1694,8 +1824,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1717,116 +1855,170 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2969782616500465</v>
+        <v>0.4471507958364636</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1915899776092681</v>
+        <v>0.3633257578685733</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2373685107779348</v>
+        <v>0.4312248522677639</v>
       </c>
       <c r="E3" s="4">
-        <v>87.4903874593313</v>
+        <v>81.22153209109723</v>
       </c>
       <c r="F3" s="4">
-        <v>86.95627857212254</v>
+        <v>81.37219142106869</v>
       </c>
       <c r="G3" s="5">
         <v>92</v>
       </c>
       <c r="H3" s="5">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J3" s="5">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2115630223118111</v>
+      </c>
+      <c r="O3" s="5">
+        <v>59</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4341399598218734</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3142446253016632</v>
+      </c>
+      <c r="R3" s="5">
+        <v>59</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2570748440367747</v>
+        <v>0.382695454478046</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2176600319996218</v>
+        <v>0.3076022580118234</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2167933748196444</v>
+        <v>0.321742117280569</v>
       </c>
       <c r="E4" s="4">
-        <v>87.6602564102563</v>
+        <v>84.07116692830955</v>
       </c>
       <c r="F4" s="4">
-        <v>86.80949922560741</v>
+        <v>84.88276544484606</v>
       </c>
       <c r="G4" s="5">
         <v>52</v>
       </c>
       <c r="H4" s="5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I4" s="5">
         <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.01489974066356044</v>
+      </c>
+      <c r="O4" s="5">
+        <v>45</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3821223875294475</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3055704751940651</v>
+      </c>
+      <c r="R4" s="5">
+        <v>44</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.945520882191469</v>
+        <v>0.7451306768713266</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>0.3784777737611194</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4810794622225103</v>
+        <v>0.6007600258313156</v>
       </c>
       <c r="E5" s="4">
-        <v>64.73922902494334</v>
+        <v>74.7732426303856</v>
       </c>
       <c r="F5" s="4">
-        <v>47.81506338553346</v>
+        <v>68.92617449664387</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -1840,50 +2032,82 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7451306768713266</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3784777737611194</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3442148297045833</v>
+        <v>0.2536770892897569</v>
       </c>
       <c r="C6" s="4">
-        <v>0.06903715118892251</v>
+        <v>0.09360926171876827</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1800059548783111</v>
+        <v>0.3821865788864898</v>
       </c>
       <c r="E6" s="4">
-        <v>88.4126984126984</v>
+        <v>85.13605442176869</v>
       </c>
       <c r="F6" s="4">
-        <v>72.55033557046885</v>
+        <v>80.36539895600335</v>
       </c>
       <c r="G6" s="5">
         <v>3</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
         <v>1</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2536770892897569</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.09360926171876827</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1894,6 +2118,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1901,7 +2126,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1912,9 +2137,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1948,8 +2179,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1971,107 +2210,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2670788602886969</v>
+        <v>0.3326681399481179</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1860786947534826</v>
+        <v>0.1574533365298825</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1819979314258344</v>
+        <v>0.2000317807008546</v>
       </c>
       <c r="E3" s="4">
-        <v>90.28356994971944</v>
+        <v>89.41807157645688</v>
       </c>
       <c r="F3" s="4">
-        <v>90.04826865090868</v>
+        <v>89.32727847485678</v>
       </c>
       <c r="G3" s="5">
         <v>92</v>
       </c>
       <c r="H3" s="5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I3" s="5">
         <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L3" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.02325222024716312</v>
+      </c>
+      <c r="O3" s="5">
+        <v>75</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.332068559783141</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1607482363703523</v>
+      </c>
+      <c r="R3" s="5">
+        <v>75</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2571916669920019</v>
+        <v>0.1901769153499109</v>
       </c>
       <c r="C4" s="4">
-        <v>0.22196779065023</v>
+        <v>0.1719733632622261</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2297640486718303</v>
+        <v>0.172103677998634</v>
       </c>
       <c r="E4" s="4">
-        <v>90.9648090005232</v>
+        <v>90.41339612768152</v>
       </c>
       <c r="F4" s="4">
-        <v>92.19110308036528</v>
+        <v>91.19880399242926</v>
       </c>
       <c r="G4" s="5">
         <v>52</v>
       </c>
       <c r="H4" s="5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I4" s="5">
         <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1022612108608574</v>
+      </c>
+      <c r="O4" s="5">
+        <v>49</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1718686305196826</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1588050534950976</v>
+      </c>
+      <c r="R4" s="5">
+        <v>49</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6580295352595916</v>
+        <v>0.6649969520836905</v>
       </c>
       <c r="C5" s="4">
-        <v>0.9219792052343792</v>
+        <v>0.8451054879623889</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6154137085400558</v>
+        <v>0.5481892231199433</v>
       </c>
       <c r="E5" s="4">
-        <v>85.66893424036282</v>
+        <v>85.40816326530617</v>
       </c>
       <c r="F5" s="4">
-        <v>82.07307979120063</v>
+        <v>82.95302013422808</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
@@ -2094,50 +2387,82 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6649969520836905</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8451054879623889</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.008702032666823</v>
+        <v>0.2180256017020499</v>
       </c>
       <c r="C6" s="4">
-        <v>0</v>
+        <v>0.2717138494836493</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1780243644132421</v>
+        <v>0.1587259276972919</v>
       </c>
       <c r="E6" s="4">
-        <v>77.99319727891161</v>
+        <v>89.30839002267574</v>
       </c>
       <c r="F6" s="4">
-        <v>50.20507084265464</v>
+        <v>79.61595824011961</v>
       </c>
       <c r="G6" s="5">
         <v>3</v>
       </c>
       <c r="H6" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
         <v>1</v>
       </c>
       <c r="J6" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2180256017020499</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2717138494836493</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2148,6 +2473,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2155,7 +2481,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2166,9 +2492,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2202,8 +2534,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2225,66 +2565,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.293152818536406</v>
+        <v>0.2969782616500465</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1484037832389985</v>
+        <v>0.1915899776092681</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2160206748222725</v>
+        <v>0.2373685107779348</v>
       </c>
       <c r="E3" s="4">
-        <v>85.66844128955981</v>
+        <v>87.4903874593313</v>
       </c>
       <c r="F3" s="4">
-        <v>85.99479622604748</v>
+        <v>86.95627857212254</v>
       </c>
       <c r="G3" s="5">
         <v>92</v>
       </c>
       <c r="H3" s="5">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>17</v>
+      </c>
+      <c r="K3" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
+      <c r="L3" s="5">
         <v>14</v>
       </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>13</v>
-      </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.002376925883524642</v>
+      </c>
+      <c r="O3" s="5">
+        <v>74</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.296668227839152</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1917827013295539</v>
+      </c>
+      <c r="R3" s="5">
+        <v>74</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3317435945112989</v>
+        <v>0.2570748440367747</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2769371128955104</v>
+        <v>0.2176600319996218</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3166077597815088</v>
+        <v>0.2167933748196444</v>
       </c>
       <c r="E4" s="4">
-        <v>87.36002093144907</v>
+        <v>87.6602564102563</v>
       </c>
       <c r="F4" s="4">
-        <v>88.83970056788831</v>
+        <v>86.80949922560741</v>
       </c>
       <c r="G4" s="5">
         <v>52</v>
@@ -2293,10 +2669,10 @@
         <v>46</v>
       </c>
       <c r="I4" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -2305,93 +2681,139 @@
         <v>1</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.08253746296981251</v>
+      </c>
+      <c r="O4" s="5">
+        <v>46</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2398171340757156</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2053284870844951</v>
+      </c>
+      <c r="R4" s="5">
+        <v>46</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5710015340469378</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.7601337976536797</v>
-      </c>
+        <v>0.945520882191469</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.5446533248709405</v>
+        <v>0.4810794622225103</v>
       </c>
       <c r="E5" s="4">
-        <v>78.26530612244898</v>
+        <v>64.73922902494334</v>
       </c>
       <c r="F5" s="4">
-        <v>72.20357941834462</v>
+        <v>47.81506338553346</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.945520882191469</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.5156018663460221</v>
+        <v>0.3442148297045833</v>
       </c>
       <c r="C6" s="4">
-        <v>0.5049115419970462</v>
+        <v>0.06903715118892251</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3487788765643245</v>
+        <v>0.1800059548783111</v>
       </c>
       <c r="E6" s="4">
-        <v>87.32426303854872</v>
+        <v>88.4126984126984</v>
       </c>
       <c r="F6" s="4">
-        <v>77.2595078299762</v>
+        <v>72.55033557046885</v>
       </c>
       <c r="G6" s="5">
         <v>3</v>
       </c>
       <c r="H6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="5">
         <v>1</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3442148297045833</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.06903715118892251</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2402,6 +2824,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2409,7 +2832,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2420,9 +2843,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2456,8 +2885,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2479,107 +2916,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.005880020852677</v>
+        <v>0.2670788602886969</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3423653451846094</v>
+        <v>0.1860786947534826</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6327944403787993</v>
+        <v>0.1819979314258344</v>
       </c>
       <c r="E3" s="4">
-        <v>64.89167406092884</v>
+        <v>90.28356994971944</v>
       </c>
       <c r="F3" s="4">
-        <v>69.81008656745487</v>
+        <v>90.04826865090868</v>
       </c>
       <c r="G3" s="5">
         <v>92</v>
       </c>
       <c r="H3" s="5">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K3" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1552157837479711</v>
+      </c>
+      <c r="O3" s="5">
+        <v>77</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2200549455222731</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1812431830926312</v>
+      </c>
+      <c r="R3" s="5">
+        <v>77</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4163704524917695</v>
+        <v>0.2571916669920019</v>
       </c>
       <c r="C4" s="4">
-        <v>0.22550243068825</v>
+        <v>0.22196779065023</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3977850297248083</v>
+        <v>0.2297640486718303</v>
       </c>
       <c r="E4" s="4">
-        <v>65.50758765044468</v>
+        <v>90.9648090005232</v>
       </c>
       <c r="F4" s="4">
-        <v>75.14691963517521</v>
+        <v>92.19110308036528</v>
       </c>
       <c r="G4" s="5">
         <v>52</v>
       </c>
       <c r="H4" s="5">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1272370325472017</v>
+      </c>
+      <c r="O4" s="5">
+        <v>48</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.189356356790805</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1194731013898724</v>
+      </c>
+      <c r="R4" s="5">
+        <v>47</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.278486633680321</v>
+        <v>0.6580295352595916</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7001665542496482</v>
+        <v>0.9219792052343792</v>
       </c>
       <c r="D5" s="4">
-        <v>1.225861563664845</v>
+        <v>0.6154137085400558</v>
       </c>
       <c r="E5" s="4">
-        <v>81.66666666666667</v>
+        <v>85.66893424036282</v>
       </c>
       <c r="F5" s="4">
-        <v>81.88665175242352</v>
+        <v>82.07307979120063</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
@@ -2597,55 +3088,83 @@
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6580295352595916</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.9219792052343792</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.8355227382746921</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.1948877487710092</v>
-      </c>
+        <v>1.008702032666823</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>0.2262670915312726</v>
+        <v>0.1780243644132421</v>
       </c>
       <c r="E6" s="4">
-        <v>75.31746031746033</v>
+        <v>77.99319727891161</v>
       </c>
       <c r="F6" s="4">
-        <v>68.52721849366165</v>
+        <v>50.20507084265464</v>
       </c>
       <c r="G6" s="5">
         <v>3</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <v>1</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.008702032666823</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2656,6 +3175,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2663,7 +3183,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2674,9 +3194,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2710,8 +3236,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2733,107 +3267,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4104640043207784</v>
+        <v>0.293152818536406</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3525957846919497</v>
+        <v>0.1484037832389985</v>
       </c>
       <c r="D3" s="4">
-        <v>0.381187487546357</v>
+        <v>0.2160206748222725</v>
       </c>
       <c r="E3" s="4">
-        <v>94.56965394853613</v>
+        <v>85.66844128955981</v>
       </c>
       <c r="F3" s="4">
-        <v>94.60242194339152</v>
+        <v>85.99479622604748</v>
       </c>
       <c r="G3" s="5">
         <v>92</v>
       </c>
       <c r="H3" s="5">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.05427018664199144</v>
+      </c>
+      <c r="O3" s="5">
+        <v>75</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2816930868548476</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1444383760694275</v>
+      </c>
+      <c r="R3" s="5">
+        <v>75</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5092949234848777</v>
+        <v>0.3317435945112989</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4535083425186668</v>
+        <v>0.2769371128955104</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4924621448247188</v>
+        <v>0.3166077597815088</v>
       </c>
       <c r="E4" s="4">
-        <v>92.8107012035579</v>
+        <v>87.36002093144907</v>
       </c>
       <c r="F4" s="4">
-        <v>92.38620719325517</v>
+        <v>88.83970056788831</v>
       </c>
       <c r="G4" s="5">
         <v>52</v>
       </c>
       <c r="H4" s="5">
+        <v>46</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2227923727571278</v>
+      </c>
+      <c r="O4" s="5">
         <v>47</v>
       </c>
-      <c r="I4" s="5">
-        <v>3</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="P4" s="4">
+        <v>0.2046171322294693</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1526021879471054</v>
+      </c>
+      <c r="R4" s="5">
+        <v>46</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.173804943147341</v>
+        <v>0.5710015340469378</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6436060378927095</v>
+        <v>0.7601337976536797</v>
       </c>
       <c r="D5" s="4">
-        <v>1.109787587704649</v>
+        <v>0.5446533248709405</v>
       </c>
       <c r="E5" s="4">
-        <v>93.15192743764173</v>
+        <v>78.26530612244898</v>
       </c>
       <c r="F5" s="4">
-        <v>88.709917971663</v>
+        <v>72.20357941834462</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
@@ -2851,55 +3439,87 @@
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5710015340469378</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7601337976536797</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.394820851983577</v>
+        <v>0.5156018663460221</v>
       </c>
       <c r="C6" s="4">
-        <v>0.6059496190035816</v>
+        <v>0.5049115419970462</v>
       </c>
       <c r="D6" s="4">
-        <v>0.6583535203356661</v>
+        <v>0.3487788765643245</v>
       </c>
       <c r="E6" s="4">
-        <v>84.51247165532877</v>
+        <v>87.32426303854872</v>
       </c>
       <c r="F6" s="4">
-        <v>62.94183445190232</v>
+        <v>77.2595078299762</v>
       </c>
       <c r="G6" s="5">
         <v>3</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
         <v>1</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5156018663460221</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.5049115419970462</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2910,6 +3530,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2917,7 +3538,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2928,9 +3549,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2964,8 +3591,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2987,148 +3622,218 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.154617457092951</v>
+        <v>1.005880020852677</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3966391543250736</v>
+        <v>0.3423653451846094</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6586935744633985</v>
+        <v>0.6327944403787993</v>
       </c>
       <c r="E3" s="4">
-        <v>56.18456078083393</v>
+        <v>64.89167406092884</v>
       </c>
       <c r="F3" s="4">
-        <v>63.12664137729784</v>
+        <v>69.81008656745487</v>
       </c>
       <c r="G3" s="5">
         <v>92</v>
       </c>
       <c r="H3" s="5">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I3" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L3" s="5">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1298536219418279</v>
+      </c>
+      <c r="O3" s="5">
+        <v>54</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.009338347832962</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2857351954012516</v>
+      </c>
+      <c r="R3" s="5">
+        <v>54</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5698682608813086</v>
+        <v>0.4163704524917695</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3689640438967313</v>
+        <v>0.22550243068825</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5023310020255741</v>
+        <v>0.3977850297248083</v>
       </c>
       <c r="E4" s="4">
-        <v>57.06763474620608</v>
+        <v>65.50758765044468</v>
       </c>
       <c r="F4" s="4">
-        <v>67.25972293925334</v>
+        <v>75.14691963517521</v>
       </c>
       <c r="G4" s="5">
         <v>52</v>
       </c>
       <c r="H4" s="5">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.07119933558342251</v>
+      </c>
+      <c r="O4" s="5">
+        <v>40</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3933626616571274</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1920323358240442</v>
+      </c>
+      <c r="R4" s="5">
+        <v>40</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.740229699067451</v>
+        <v>1.278486633680321</v>
       </c>
       <c r="C5" s="4">
-        <v>0.740229699067451</v>
+        <v>0.7001665542496482</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6720804105721072</v>
+        <v>1.225861563664845</v>
       </c>
       <c r="E5" s="4">
-        <v>79.96598639455783</v>
+        <v>81.66666666666667</v>
       </c>
       <c r="F5" s="4">
-        <v>77.70693512304251</v>
+        <v>81.88665175242352</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>3</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="P5" s="4">
+        <v>1.278486633680321</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7001665542496482</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.669541442668292</v>
+        <v>0.8355227382746921</v>
       </c>
       <c r="C6" s="4">
-        <v>0.7875218008088609</v>
+        <v>0.1948877487710092</v>
       </c>
       <c r="D6" s="4">
-        <v>0.5334992528940301</v>
+        <v>0.2262670915312726</v>
       </c>
       <c r="E6" s="4">
-        <v>77.58503401360545</v>
+        <v>75.31746031746033</v>
       </c>
       <c r="F6" s="4">
-        <v>61.05518269947731</v>
+        <v>68.52721849366165</v>
       </c>
       <c r="G6" s="5">
         <v>3</v>
@@ -3143,17 +3848,33 @@
         <v>1</v>
       </c>
       <c r="K6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.8355227382746921</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1948877487710092</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3164,6 +3885,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3171,7 +3893,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3182,9 +3904,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3218,8 +3946,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3241,75 +3977,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4001940532214043</v>
+        <v>0.4104640043207784</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3170622544711692</v>
+        <v>0.3525957846919497</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3385658399197954</v>
+        <v>0.381187487546357</v>
       </c>
       <c r="E3" s="4">
-        <v>92.09701271813057</v>
+        <v>94.56965394853613</v>
       </c>
       <c r="F3" s="4">
-        <v>91.80429919268595</v>
+        <v>94.60242194339152</v>
       </c>
       <c r="G3" s="5">
         <v>92</v>
       </c>
       <c r="H3" s="5">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
         <v>4</v>
       </c>
-      <c r="J3" s="5">
-        <v>5</v>
-      </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3504856435135895</v>
+      </c>
+      <c r="O3" s="5">
+        <v>88</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2058414592026272</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1546033804099548</v>
+      </c>
+      <c r="R3" s="5">
+        <v>88</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3820175933476616</v>
+        <v>0.5092949234848777</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3625561865527489</v>
+        <v>0.4535083425186668</v>
       </c>
       <c r="D4" s="4">
-        <v>0.347357721086283</v>
+        <v>0.4924621448247188</v>
       </c>
       <c r="E4" s="4">
-        <v>91.21860282574528</v>
+        <v>92.8107012035579</v>
       </c>
       <c r="F4" s="4">
-        <v>91.53329891585167</v>
+        <v>92.38620719325517</v>
       </c>
       <c r="G4" s="5">
         <v>52</v>
       </c>
       <c r="H4" s="5">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
         <v>2</v>
@@ -3323,75 +4095,109 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.423838599570429</v>
+      </c>
+      <c r="O4" s="5">
+        <v>47</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1499539934310444</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1010288666687266</v>
+      </c>
+      <c r="R4" s="5">
+        <v>47</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6479694332568423</v>
+        <v>1.173804943147341</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6479694332568423</v>
+        <v>0.6436060378927095</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6464913572761191</v>
+        <v>1.109787587704649</v>
       </c>
       <c r="E5" s="4">
-        <v>92.09750566893422</v>
+        <v>93.15192743764173</v>
       </c>
       <c r="F5" s="4">
-        <v>87.85980611483961</v>
+        <v>88.709917971663</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>3</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="P5" s="4">
+        <v>1.173804943147341</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6436060378927095</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.225188655556693</v>
+        <v>1.394820851983577</v>
       </c>
       <c r="C6" s="4">
-        <v>0</v>
+        <v>0.6059496190035816</v>
       </c>
       <c r="D6" s="4">
-        <v>0.5290498166301963</v>
+        <v>0.6583535203356661</v>
       </c>
       <c r="E6" s="4">
-        <v>80.71428571428582</v>
+        <v>84.51247165532877</v>
       </c>
       <c r="F6" s="4">
-        <v>53.07606263982042</v>
+        <v>62.94183445190232</v>
       </c>
       <c r="G6" s="5">
         <v>3</v>
       </c>
       <c r="H6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="5">
         <v>1</v>
@@ -3405,9 +4211,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.394820851983577</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6059496190035816</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3418,12 +4240,1576 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.154617457092951</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3966391543250736</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6586935744633985</v>
+      </c>
+      <c r="E3" s="4">
+        <v>56.18456078083393</v>
+      </c>
+      <c r="F3" s="4">
+        <v>63.12664137729784</v>
+      </c>
+      <c r="G3" s="5">
+        <v>92</v>
+      </c>
+      <c r="H3" s="5">
+        <v>47</v>
+      </c>
+      <c r="I3" s="5">
+        <v>8</v>
+      </c>
+      <c r="J3" s="5">
+        <v>37</v>
+      </c>
+      <c r="K3" s="5">
+        <v>5</v>
+      </c>
+      <c r="L3" s="5">
+        <v>32</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.1443186545693822</v>
+      </c>
+      <c r="O3" s="5">
+        <v>47</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.165336113811404</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3433539093687638</v>
+      </c>
+      <c r="R3" s="5">
+        <v>47</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5698682608813086</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3689640438967313</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5023310020255741</v>
+      </c>
+      <c r="E4" s="4">
+        <v>57.06763474620608</v>
+      </c>
+      <c r="F4" s="4">
+        <v>67.25972293925334</v>
+      </c>
+      <c r="G4" s="5">
+        <v>52</v>
+      </c>
+      <c r="H4" s="5">
+        <v>33</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>17</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>16</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.3208011302572182</v>
+      </c>
+      <c r="O4" s="5">
+        <v>33</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5440667852861033</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2265130811863067</v>
+      </c>
+      <c r="R4" s="5">
+        <v>33</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.740229699067451</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.740229699067451</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.6720804105721072</v>
+      </c>
+      <c r="E5" s="4">
+        <v>79.96598639455783</v>
+      </c>
+      <c r="F5" s="4">
+        <v>77.70693512304251</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.740229699067451</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.740229699067451</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.669541442668292</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.7875218008088609</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.5334992528940301</v>
+      </c>
+      <c r="E6" s="4">
+        <v>77.58503401360545</v>
+      </c>
+      <c r="F6" s="4">
+        <v>61.05518269947731</v>
+      </c>
+      <c r="G6" s="5">
+        <v>3</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.669541442668292</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.7875218008088609</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4001940532214043</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3170622544711692</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3385658399197954</v>
+      </c>
+      <c r="E3" s="4">
+        <v>92.09701271813057</v>
+      </c>
+      <c r="F3" s="4">
+        <v>91.80429919268595</v>
+      </c>
+      <c r="G3" s="5">
+        <v>92</v>
+      </c>
+      <c r="H3" s="5">
+        <v>83</v>
+      </c>
+      <c r="I3" s="5">
+        <v>4</v>
+      </c>
+      <c r="J3" s="5">
+        <v>5</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>5</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3030884685775703</v>
+      </c>
+      <c r="O3" s="5">
+        <v>83</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2501357122415683</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1835975417850635</v>
+      </c>
+      <c r="R3" s="5">
+        <v>83</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3820175933476616</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3625561865527489</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.347357721086283</v>
+      </c>
+      <c r="E4" s="4">
+        <v>91.21860282574528</v>
+      </c>
+      <c r="F4" s="4">
+        <v>91.53329891585167</v>
+      </c>
+      <c r="G4" s="5">
+        <v>52</v>
+      </c>
+      <c r="H4" s="5">
+        <v>49</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2897483402315749</v>
+      </c>
+      <c r="O4" s="5">
+        <v>49</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1595933393258485</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.10406034119885</v>
+      </c>
+      <c r="R4" s="5">
+        <v>48</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6479694332568423</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.6479694332568423</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.6464913572761191</v>
+      </c>
+      <c r="E5" s="4">
+        <v>92.09750566893422</v>
+      </c>
+      <c r="F5" s="4">
+        <v>87.85980611483961</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6479694332568423</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6479694332568423</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1.225188655556693</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
+        <v>0.5290498166301963</v>
+      </c>
+      <c r="E6" s="4">
+        <v>80.71428571428582</v>
+      </c>
+      <c r="F6" s="4">
+        <v>53.07606263982042</v>
+      </c>
+      <c r="G6" s="5">
+        <v>3</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>2</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.225188655556693</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>69.33333333333334</v>
+      </c>
+      <c r="C3" s="3">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3">
+        <v>22.66666666666666</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>22.66666666666666</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.3413113538540912</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.220082043142951</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.2799742949122797</v>
+      </c>
+      <c r="K3" s="4">
+        <v>78.77165532879779</v>
+      </c>
+      <c r="L3" s="4">
+        <v>80.11409395973129</v>
+      </c>
+      <c r="M3" s="5">
+        <v>150</v>
+      </c>
+      <c r="N3" s="5">
+        <v>774920.4216003418</v>
+      </c>
+      <c r="O3" s="4">
+        <v>31.9475767480352</v>
+      </c>
+      <c r="P3" s="5">
+        <v>24256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>58.66666666666666</v>
+      </c>
+      <c r="C4" s="3">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="D4" s="3">
+        <v>28.66666666666667</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="F4" s="3">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="G4" s="3">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.097649705016846</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.5556638578471638</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1.180437216081934</v>
+      </c>
+      <c r="K4" s="4">
+        <v>81.90634920634926</v>
+      </c>
+      <c r="L4" s="4">
+        <v>79.96129753914992</v>
+      </c>
+      <c r="M4" s="5">
+        <v>150</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1432828.38010788</v>
+      </c>
+      <c r="O4" s="4">
+        <v>49.68542825812746</v>
+      </c>
+      <c r="P4" s="5">
+        <v>28838</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>87.33333333333333</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="D5" s="3">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="F5" s="3">
+        <v>8.666666666666668</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.3160247935454956</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2048511129716927</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2645581233348713</v>
+      </c>
+      <c r="K5" s="4">
+        <v>87.02789115646294</v>
+      </c>
+      <c r="L5" s="4">
+        <v>88.07143922446004</v>
+      </c>
+      <c r="M5" s="5">
+        <v>150</v>
+      </c>
+      <c r="N5" s="5">
+        <v>3327495.409250259</v>
+      </c>
+      <c r="O5" s="4">
+        <v>132.4481713668853</v>
+      </c>
+      <c r="P5" s="5">
+        <v>25123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>80</v>
+      </c>
+      <c r="C6" s="3">
+        <v>7.333333333333333</v>
+      </c>
+      <c r="D6" s="3">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="F6" s="3">
+        <v>12</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.298168424783687</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2332432099587303</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2774532374712938</v>
+      </c>
+      <c r="K6" s="4">
+        <v>85.31678004535165</v>
+      </c>
+      <c r="L6" s="4">
+        <v>84.06689038031233</v>
+      </c>
+      <c r="M6" s="5">
+        <v>150</v>
+      </c>
+      <c r="N6" s="5">
+        <v>2055755.521774292</v>
+      </c>
+      <c r="O6" s="4">
+        <v>85.39318442196111</v>
+      </c>
+      <c r="P6" s="5">
+        <v>24074</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>88.66666666666667</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7.333333333333333</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1927166858575508</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1330460883324069</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1604469317728042</v>
+      </c>
+      <c r="K7" s="4">
+        <v>90.42925170068015</v>
+      </c>
+      <c r="L7" s="4">
+        <v>90.71588366890366</v>
+      </c>
+      <c r="M7" s="5">
+        <v>150</v>
+      </c>
+      <c r="N7" s="5">
+        <v>4855341.718435287</v>
+      </c>
+      <c r="O7" s="4">
+        <v>205.5258092801934</v>
+      </c>
+      <c r="P7" s="5">
+        <v>23624</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>82</v>
+      </c>
+      <c r="C8" s="3">
+        <v>8</v>
+      </c>
+      <c r="D8" s="3">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="F8" s="3">
+        <v>8.666666666666668</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.3534307674664469</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2539940492827608</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2770661388025399</v>
+      </c>
+      <c r="K8" s="4">
+        <v>86.4476190476192</v>
+      </c>
+      <c r="L8" s="4">
+        <v>85.71536167039585</v>
+      </c>
+      <c r="M8" s="5">
+        <v>150</v>
+      </c>
+      <c r="N8" s="5">
+        <v>371415.370464325</v>
+      </c>
+      <c r="O8" s="4">
+        <v>13.93940215666447</v>
+      </c>
+      <c r="P8" s="5">
+        <v>26645</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="C9" s="3">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3">
+        <v>19.33333333333333</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="F9" s="3">
+        <v>18</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4187177583575126</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3070870764012797</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.3570810076594037</v>
+      </c>
+      <c r="K9" s="4">
+        <v>82.15873015873031</v>
+      </c>
+      <c r="L9" s="4">
+        <v>82.32013422818737</v>
+      </c>
+      <c r="M9" s="5">
+        <v>150</v>
+      </c>
+      <c r="N9" s="5">
+        <v>711925.9693622589</v>
+      </c>
+      <c r="O9" s="4">
+        <v>28.03299611601271</v>
+      </c>
+      <c r="P9" s="5">
+        <v>25396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>85.33333333333334</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D10" s="3">
+        <v>11.33333333333333</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F10" s="3">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.2809102929895312</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1724312814369397</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1997015852861663</v>
+      </c>
+      <c r="K10" s="4">
+        <v>89.68072562358273</v>
+      </c>
+      <c r="L10" s="4">
+        <v>89.65436241610755</v>
+      </c>
+      <c r="M10" s="5">
+        <v>150</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2150707.7729702</v>
+      </c>
+      <c r="O10" s="4">
+        <v>86.9043063265799</v>
+      </c>
+      <c r="P10" s="5">
+        <v>24748</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>80.66666666666666</v>
+      </c>
+      <c r="C11" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D11" s="3">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2908878337921823</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1959179128550635</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2300751838357041</v>
+      </c>
+      <c r="K11" s="4">
+        <v>87.11269841269835</v>
+      </c>
+      <c r="L11" s="4">
+        <v>85.83445190156607</v>
+      </c>
+      <c r="M11" s="5">
+        <v>150</v>
+      </c>
+      <c r="N11" s="5">
+        <v>1199898.225307465</v>
+      </c>
+      <c r="O11" s="4">
+        <v>43.45567960696308</v>
+      </c>
+      <c r="P11" s="5">
+        <v>27612</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>84</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D12" s="3">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="F12" s="3">
+        <v>11.33333333333333</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2339452016330015</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1699596767771853</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1766604369198356</v>
+      </c>
+      <c r="K12" s="4">
+        <v>90.18163265306174</v>
+      </c>
+      <c r="L12" s="4">
+        <v>89.83475018642699</v>
+      </c>
+      <c r="M12" s="5">
+        <v>150</v>
+      </c>
+      <c r="N12" s="5">
+        <v>443293.7927246094</v>
+      </c>
+      <c r="O12" s="4">
+        <v>22.90923993408834</v>
+      </c>
+      <c r="P12" s="5">
+        <v>19350</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C13" s="3">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="D13" s="3">
+        <v>11.33333333333333</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="F13" s="3">
+        <v>10</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.2654377671183818</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1630613562406029</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2209061411446297</v>
+      </c>
+      <c r="K13" s="4">
+        <v>86.13990929705218</v>
+      </c>
+      <c r="L13" s="4">
+        <v>86.53049962714336</v>
+      </c>
+      <c r="M13" s="5">
+        <v>150</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2045763.631820679</v>
+      </c>
+      <c r="O13" s="4">
+        <v>81.19398443485787</v>
+      </c>
+      <c r="P13" s="5">
+        <v>25196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>64.66666666666666</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D14" s="3">
+        <v>32</v>
+      </c>
+      <c r="E14" s="3">
+        <v>8.666666666666668</v>
+      </c>
+      <c r="F14" s="3">
+        <v>22.66666666666666</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.7977067634844542</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.25470324579278</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.5206484418501753</v>
+      </c>
+      <c r="K14" s="4">
+        <v>65.64920634920631</v>
+      </c>
+      <c r="L14" s="4">
+        <v>71.87606263982104</v>
+      </c>
+      <c r="M14" s="5">
+        <v>150</v>
+      </c>
+      <c r="N14" s="5">
+        <v>14011773.94533157</v>
+      </c>
+      <c r="O14" s="4">
+        <v>286.2057304436868</v>
+      </c>
+      <c r="P14" s="5">
+        <v>48957</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>92</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="F15" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2296059952696585</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.146714608002139</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1920989003266503</v>
+      </c>
+      <c r="K15" s="4">
+        <v>93.73038548752803</v>
+      </c>
+      <c r="L15" s="4">
+        <v>93.08307233407837</v>
+      </c>
+      <c r="M15" s="5">
+        <v>150</v>
+      </c>
+      <c r="N15" s="5">
+        <v>4222422.600746155</v>
+      </c>
+      <c r="O15" s="4">
+        <v>299.2927842887833</v>
+      </c>
+      <c r="P15" s="5">
+        <v>14108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="C16" s="3">
+        <v>7.333333333333333</v>
+      </c>
+      <c r="D16" s="3">
+        <v>36.66666666666666</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4</v>
+      </c>
+      <c r="F16" s="3">
+        <v>32.66666666666666</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.9315447248715587</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.3169140037796576</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.5613040708695983</v>
+      </c>
+      <c r="K16" s="4">
+        <v>57.39433106575969</v>
+      </c>
+      <c r="L16" s="4">
+        <v>64.80961968680087</v>
+      </c>
+      <c r="M16" s="5">
+        <v>150</v>
+      </c>
+      <c r="N16" s="5">
+        <v>4302101.472139359</v>
+      </c>
+      <c r="O16" s="4">
+        <v>95.59588187763835</v>
+      </c>
+      <c r="P16" s="5">
+        <v>45003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>89.33333333333333</v>
+      </c>
+      <c r="C17" s="3">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="D17" s="3">
+        <v>6</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2462054229173934</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.165502989891609</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1978076080321659</v>
+      </c>
+      <c r="K17" s="4">
+        <v>91.56485260770958</v>
+      </c>
+      <c r="L17" s="4">
+        <v>90.85689783743354</v>
+      </c>
+      <c r="M17" s="5">
+        <v>150</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1478746.902227402</v>
+      </c>
+      <c r="O17" s="4">
+        <v>102.3283442133694</v>
+      </c>
+      <c r="P17" s="5">
+        <v>14451</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3581,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
@@ -3628,7 +6014,7 @@
         <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
@@ -3669,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
         <v>16</v>
@@ -3713,16 +6099,16 @@
         <v>1</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
       <c r="N7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25" customHeight="1">
@@ -3757,10 +6143,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -3801,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" s="5">
         <v>22</v>
@@ -3845,10 +6231,10 @@
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
@@ -3889,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -3933,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
         <v>16</v>
@@ -3977,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="5">
         <v>14</v>
@@ -4021,16 +6407,16 @@
         <v>8</v>
       </c>
       <c r="K14" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -4065,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="5">
         <v>3</v>
@@ -4109,16 +6495,16 @@
         <v>3</v>
       </c>
       <c r="K16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M16" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -4178,9 +6564,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>104</v>
+      </c>
+      <c r="C3" s="5">
+        <v>12</v>
+      </c>
+      <c r="D3" s="5">
+        <v>34</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>34</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>29</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>88</v>
+      </c>
+      <c r="C4" s="5">
+        <v>19</v>
+      </c>
+      <c r="D4" s="5">
+        <v>43</v>
+      </c>
+      <c r="E4" s="5">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5">
+        <v>20</v>
+      </c>
+      <c r="G4" s="5">
+        <v>16</v>
+      </c>
+      <c r="H4" s="5">
+        <v>7</v>
+      </c>
+      <c r="I4" s="5">
+        <v>7</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>18</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>131</v>
+      </c>
+      <c r="C5" s="5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>13</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>7</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>120</v>
+      </c>
+      <c r="C6" s="5">
+        <v>11</v>
+      </c>
+      <c r="D6" s="5">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <v>18</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>16</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>133</v>
+      </c>
+      <c r="C7" s="5">
+        <v>6</v>
+      </c>
+      <c r="D7" s="5">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5">
+        <v>3</v>
+      </c>
+      <c r="F7" s="5">
+        <v>7</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>3</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>6</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>123</v>
+      </c>
+      <c r="C8" s="5">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5">
+        <v>15</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2</v>
+      </c>
+      <c r="F8" s="5">
+        <v>13</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>2</v>
+      </c>
+      <c r="I8" s="5">
+        <v>2</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5">
+        <v>9</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>106</v>
+      </c>
+      <c r="C9" s="5">
+        <v>15</v>
+      </c>
+      <c r="D9" s="5">
+        <v>29</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>27</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5">
+        <v>22</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>128</v>
+      </c>
+      <c r="C10" s="5">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5">
+        <v>17</v>
+      </c>
+      <c r="E10" s="5">
+        <v>5</v>
+      </c>
+      <c r="F10" s="5">
+        <v>12</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>5</v>
+      </c>
+      <c r="I10" s="5">
+        <v>5</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5">
+        <v>6</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>121</v>
+      </c>
+      <c r="C11" s="5">
+        <v>10</v>
+      </c>
+      <c r="D11" s="5">
+        <v>19</v>
+      </c>
+      <c r="E11" s="5">
+        <v>3</v>
+      </c>
+      <c r="F11" s="5">
+        <v>16</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>3</v>
+      </c>
+      <c r="I11" s="5">
+        <v>3</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>14</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>126</v>
+      </c>
+      <c r="C12" s="5">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5">
+        <v>19</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5">
+        <v>17</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>16</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>125</v>
+      </c>
+      <c r="C13" s="5">
+        <v>8</v>
+      </c>
+      <c r="D13" s="5">
+        <v>17</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5">
+        <v>15</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <v>14</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>97</v>
+      </c>
+      <c r="C14" s="5">
+        <v>5</v>
+      </c>
+      <c r="D14" s="5">
+        <v>48</v>
+      </c>
+      <c r="E14" s="5">
+        <v>13</v>
+      </c>
+      <c r="F14" s="5">
+        <v>34</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5">
+        <v>13</v>
+      </c>
+      <c r="I14" s="5">
+        <v>10</v>
+      </c>
+      <c r="J14" s="5">
+        <v>8</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>24</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>138</v>
+      </c>
+      <c r="C15" s="5">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5">
+        <v>8</v>
+      </c>
+      <c r="E15" s="5">
+        <v>2</v>
+      </c>
+      <c r="F15" s="5">
+        <v>5</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5">
+        <v>2</v>
+      </c>
+      <c r="I15" s="5">
+        <v>2</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>3</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>84</v>
+      </c>
+      <c r="C16" s="5">
+        <v>11</v>
+      </c>
+      <c r="D16" s="5">
+        <v>55</v>
+      </c>
+      <c r="E16" s="5">
+        <v>6</v>
+      </c>
+      <c r="F16" s="5">
+        <v>49</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>6</v>
+      </c>
+      <c r="I16" s="5">
+        <v>5</v>
+      </c>
+      <c r="J16" s="5">
+        <v>3</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>39</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>134</v>
+      </c>
+      <c r="C17" s="5">
+        <v>7</v>
+      </c>
+      <c r="D17" s="5">
+        <v>9</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>8</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>5</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4191,9 +7332,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4227,8 +7374,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4250,10 +7405,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3907000250151388</v>
@@ -4291,10 +7464,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1103552779539539</v>
+      </c>
+      <c r="O3" s="5">
+        <v>57</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3942957001519485</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2186790235554268</v>
+      </c>
+      <c r="R3" s="5">
+        <v>57</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2519042230434861</v>
@@ -4332,17 +7523,33 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.07532231913081976</v>
+      </c>
+      <c r="O4" s="5">
+        <v>45</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2392062686247563</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2190482514754993</v>
+      </c>
+      <c r="R4" s="5">
+        <v>45</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5566201637707687</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
         <v>0.3684925822871795</v>
       </c>
@@ -4373,10 +7580,24 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5566201637707687</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.2709707347782644</v>
@@ -4414,9 +7635,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2709707347782644</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2833284139050534</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4427,14 +7664,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4445,9 +7683,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,8 +7725,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4504,10 +7756,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.281942951121603</v>
@@ -4545,10 +7815,28 @@
       <c r="M3" s="5">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.7998774803440117</v>
+      </c>
+      <c r="O3" s="5">
+        <v>58</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.472401488161479</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7764264586803147</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3529202955422409</v>
@@ -4586,17 +7874,33 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.07862271773621998</v>
+      </c>
+      <c r="O4" s="5">
+        <v>44</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.342465699162893</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3349012570140129</v>
+      </c>
+      <c r="R4" s="5">
+        <v>44</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.9130166799349126</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
         <v>0.9386450877311366</v>
       </c>
@@ -4627,17 +7931,29 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9130166799349126</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>2.879750815131843</v>
       </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
         <v>2.84166010926026</v>
       </c>
@@ -4668,9 +7984,23 @@
       <c r="M6" s="5">
         <v>2</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>2.879750815131843</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4681,14 +8011,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4699,9 +8030,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4735,8 +8072,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4758,10 +8103,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3304300082760131</v>
@@ -4799,10 +8162,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1260380636559079</v>
+      </c>
+      <c r="O3" s="5">
+        <v>77</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3033658310823035</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1966136723226317</v>
+      </c>
+      <c r="R3" s="5">
+        <v>77</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.277728730198841</v>
@@ -4840,10 +8221,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1377858294664694</v>
+      </c>
+      <c r="O4" s="5">
+        <v>50</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2442973644435555</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1773784970365255</v>
+      </c>
+      <c r="R4" s="5">
+        <v>50</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>1.581590994578808</v>
@@ -4881,10 +8280,26 @@
       <c r="M5" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.581590994578808</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7814915411717038</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.6819422124837047</v>
@@ -4922,9 +8337,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>3</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6819422124837047</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6819422124837047</v>
+      </c>
+      <c r="R6" s="5">
+        <v>3</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4935,14 +8366,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4953,9 +8385,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4989,8 +8427,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5012,10 +8458,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3055132899830025</v>
@@ -5053,10 +8517,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.009215761610058758</v>
+      </c>
+      <c r="O3" s="5">
+        <v>73</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3062863008408607</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2354575839626198</v>
+      </c>
+      <c r="R3" s="5">
+        <v>73</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2681701234537371</v>
@@ -5094,10 +8576,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.05657985342837273</v>
+      </c>
+      <c r="O4" s="5">
+        <v>44</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2505196885083327</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2258125623983473</v>
+      </c>
+      <c r="R4" s="5">
+        <v>44</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5799218603430063</v>
@@ -5135,10 +8635,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5799218603430063</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1599700070374865</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.5933782189105159</v>
@@ -5176,9 +8692,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5933782189105159</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3525294066058109</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5189,14 +8721,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5207,9 +8740,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5243,8 +8782,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5266,10 +8813,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1743251035405939</v>
@@ -5307,10 +8872,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.02695554500291967</v>
+      </c>
+      <c r="O3" s="5">
+        <v>82</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1733151506807306</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1375770171275927</v>
+      </c>
+      <c r="R3" s="5">
+        <v>82</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1759057954742685</v>
@@ -5348,10 +8931,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.03501395579928168</v>
+      </c>
+      <c r="O4" s="5">
+        <v>48</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1604445239545811</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09251338060409535</v>
+      </c>
+      <c r="R4" s="5">
+        <v>47</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.6390840893871351</v>
@@ -5389,10 +8990,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6390840893871351</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6390840893871351</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.900713834068597</v>
@@ -5430,9 +9047,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.900713834068597</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.148433187193632</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5443,514 +9076,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3636715244984057</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2519631518539493</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.261643783559553</v>
-      </c>
-      <c r="E3" s="4">
-        <v>86.73580301685841</v>
-      </c>
-      <c r="F3" s="4">
-        <v>86.30823849820034</v>
-      </c>
-      <c r="G3" s="5">
-        <v>92</v>
-      </c>
-      <c r="H3" s="5">
-        <v>75</v>
-      </c>
-      <c r="I3" s="5">
-        <v>4</v>
-      </c>
-      <c r="J3" s="5">
-        <v>13</v>
-      </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>11</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3292234900078352</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.25888597643543</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2810787510715506</v>
-      </c>
-      <c r="E4" s="4">
-        <v>86.09301412872787</v>
-      </c>
-      <c r="F4" s="4">
-        <v>85.78729994837293</v>
-      </c>
-      <c r="G4" s="5">
-        <v>52</v>
-      </c>
-      <c r="H4" s="5">
-        <v>44</v>
-      </c>
-      <c r="I4" s="5">
-        <v>6</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6600468034638093</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.100376485632296</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5639214192819656</v>
-      </c>
-      <c r="E5" s="4">
-        <v>81.4965986394558</v>
-      </c>
-      <c r="F5" s="4">
-        <v>71.67785234899375</v>
-      </c>
-      <c r="G5" s="5">
-        <v>3</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.2028008593134955</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.2770928691424031</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.2888188735862229</v>
-      </c>
-      <c r="E6" s="4">
-        <v>88.70748299319729</v>
-      </c>
-      <c r="F6" s="4">
-        <v>80.32438478747228</v>
-      </c>
-      <c r="G6" s="5">
-        <v>3</v>
-      </c>
-      <c r="H6" s="5">
-        <v>2</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4471507958364636</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3633257578685733</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4312248522677639</v>
-      </c>
-      <c r="E3" s="4">
-        <v>81.22153209109723</v>
-      </c>
-      <c r="F3" s="4">
-        <v>81.37219142106869</v>
-      </c>
-      <c r="G3" s="5">
-        <v>92</v>
-      </c>
-      <c r="H3" s="5">
-        <v>59</v>
-      </c>
-      <c r="I3" s="5">
-        <v>7</v>
-      </c>
-      <c r="J3" s="5">
-        <v>26</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>25</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.382695454478046</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3076022580118234</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.321742117280569</v>
-      </c>
-      <c r="E4" s="4">
-        <v>84.07116692830955</v>
-      </c>
-      <c r="F4" s="4">
-        <v>84.88276544484606</v>
-      </c>
-      <c r="G4" s="5">
-        <v>52</v>
-      </c>
-      <c r="H4" s="5">
-        <v>44</v>
-      </c>
-      <c r="I4" s="5">
-        <v>5</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7451306768713266</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3784777737611194</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6007600258313156</v>
-      </c>
-      <c r="E5" s="4">
-        <v>74.7732426303856</v>
-      </c>
-      <c r="F5" s="4">
-        <v>68.92617449664387</v>
-      </c>
-      <c r="G5" s="5">
-        <v>3</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.2536770892897569</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.09360926171876827</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.3821865788864898</v>
-      </c>
-      <c r="E6" s="4">
-        <v>85.13605442176869</v>
-      </c>
-      <c r="F6" s="4">
-        <v>80.36539895600335</v>
-      </c>
-      <c r="G6" s="5">
-        <v>3</v>
-      </c>
-      <c r="H6" s="5">
-        <v>2</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/BaseraImplications2025.xlsx
+++ b/public/downloads/BaseraImplications2025.xlsx
@@ -1560,16 +1560,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.009089151870302483</v>
+        <v>0.01735768343411337</v>
       </c>
       <c r="O3" s="5">
         <v>75</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3636715244984057</v>
+        <v>0.3639981863132501</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2511148310127211</v>
+        <v>0.2506647223838519</v>
       </c>
       <c r="R3" s="5">
         <v>75</v>
@@ -1619,16 +1619,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.06884394429046693</v>
+        <v>-0.01706791430655841</v>
       </c>
       <c r="O4" s="5">
         <v>44</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3263133053419577</v>
+        <v>0.326704735324227</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2648344778699112</v>
+        <v>0.2582367092147874</v>
       </c>
       <c r="R4" s="5">
         <v>44</v>
@@ -1915,16 +1915,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2115630223118111</v>
+        <v>0.2189516514172567</v>
       </c>
       <c r="O3" s="5">
         <v>59</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4341399598218734</v>
+        <v>0.4353188328055682</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3142446253016632</v>
+        <v>0.3141193942998761</v>
       </c>
       <c r="R3" s="5">
         <v>59</v>
@@ -1974,16 +1974,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.01489974066356044</v>
+        <v>0.051856400963743</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3821223875294475</v>
+        <v>0.3837136233900479</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3055704751940651</v>
+        <v>0.304091330274758</v>
       </c>
       <c r="R4" s="5">
         <v>44</v>
@@ -2270,16 +2270,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02325222024716312</v>
+        <v>0.01988457313756875</v>
       </c>
       <c r="O3" s="5">
         <v>75</v>
       </c>
       <c r="P3" s="4">
-        <v>0.332068559783141</v>
+        <v>0.3348895475272562</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1607482363703523</v>
+        <v>0.1563385204405402</v>
       </c>
       <c r="R3" s="5">
         <v>75</v>
@@ -2329,16 +2329,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1022612108608574</v>
+        <v>-0.07183947318053185</v>
       </c>
       <c r="O4" s="5">
         <v>49</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1718686305196826</v>
+        <v>0.1722189850070722</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1588050534950976</v>
+        <v>0.1573143028890421</v>
       </c>
       <c r="R4" s="5">
         <v>49</v>
@@ -2625,16 +2625,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.002376925883524642</v>
+        <v>0.02400992547120495</v>
       </c>
       <c r="O3" s="5">
         <v>74</v>
       </c>
       <c r="P3" s="4">
-        <v>0.296668227839152</v>
+        <v>0.3011111148738724</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1917827013295539</v>
+        <v>0.1908878673134612</v>
       </c>
       <c r="R3" s="5">
         <v>74</v>
@@ -2684,16 +2684,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.08253746296981251</v>
+        <v>-0.09401029807617789</v>
       </c>
       <c r="O4" s="5">
         <v>46</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2398171340757156</v>
+        <v>0.238771959729383</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2053284870844951</v>
+        <v>0.2051446234848465</v>
       </c>
       <c r="R4" s="5">
         <v>46</v>
@@ -2976,22 +2976,22 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1552157837479711</v>
+        <v>-0.1206622969213811</v>
       </c>
       <c r="O3" s="5">
         <v>77</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2200549455222731</v>
+        <v>0.2211247252556287</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1812431830926312</v>
+        <v>0.1526772701989703</v>
       </c>
       <c r="R3" s="5">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -3035,16 +3035,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1272370325472017</v>
+        <v>-0.1832342141699144</v>
       </c>
       <c r="O4" s="5">
         <v>48</v>
       </c>
       <c r="P4" s="4">
-        <v>0.189356356790805</v>
+        <v>0.1781540738715095</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1194731013898724</v>
+        <v>0.1106533744338037</v>
       </c>
       <c r="R4" s="5">
         <v>47</v>
@@ -3327,16 +3327,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05427018664199144</v>
+        <v>-0.04683421223390383</v>
       </c>
       <c r="O3" s="5">
         <v>75</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2816930868548476</v>
+        <v>0.2824665115506376</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1444383760694275</v>
+        <v>0.1440982081321946</v>
       </c>
       <c r="R3" s="5">
         <v>75</v>
@@ -3386,16 +3386,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2227923727571278</v>
+        <v>-0.2421876487475458</v>
       </c>
       <c r="O4" s="5">
         <v>47</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2046171322294693</v>
+        <v>0.202019967621936</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1526021879471054</v>
+        <v>0.1513528084768868</v>
       </c>
       <c r="R4" s="5">
         <v>46</v>
@@ -3682,16 +3682,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1298536219418279</v>
+        <v>0.1756091741038093</v>
       </c>
       <c r="O3" s="5">
         <v>54</v>
       </c>
       <c r="P3" s="4">
-        <v>1.009338347832962</v>
+        <v>1.019150411144753</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2857351954012516</v>
+        <v>0.2804215929655712</v>
       </c>
       <c r="R3" s="5">
         <v>54</v>
@@ -3741,16 +3741,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.07119933558342251</v>
+        <v>0.1401153585882611</v>
       </c>
       <c r="O4" s="5">
         <v>40</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3933626616571274</v>
+        <v>0.3865575367420825</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1920323358240442</v>
+        <v>0.1797398722842438</v>
       </c>
       <c r="R4" s="5">
         <v>40</v>
@@ -4037,16 +4037,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3504856435135895</v>
+        <v>-0.2919928033540771</v>
       </c>
       <c r="O3" s="5">
         <v>88</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2058414592026272</v>
+        <v>0.1985802320794015</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1546033804099548</v>
+        <v>0.1443533320466046</v>
       </c>
       <c r="R3" s="5">
         <v>88</v>
@@ -4096,16 +4096,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.423838599570429</v>
+        <v>-0.434545794608912</v>
       </c>
       <c r="O4" s="5">
         <v>47</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1499539934310444</v>
+        <v>0.1480017316365458</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1010288666687266</v>
+        <v>0.1000079807512476</v>
       </c>
       <c r="R4" s="5">
         <v>47</v>
@@ -4392,16 +4392,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1443186545693822</v>
+        <v>0.2191566372397915</v>
       </c>
       <c r="O3" s="5">
         <v>47</v>
       </c>
       <c r="P3" s="4">
-        <v>1.165336113811404</v>
+        <v>1.181925418615295</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3433539093687638</v>
+        <v>0.3326519998919189</v>
       </c>
       <c r="R3" s="5">
         <v>47</v>
@@ -4451,16 +4451,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3208011302572182</v>
+        <v>0.3548615244594373</v>
       </c>
       <c r="O4" s="5">
         <v>33</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5440667852861033</v>
+        <v>0.5532368914174699</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2265130811863067</v>
+        <v>0.2254809480286637</v>
       </c>
       <c r="R4" s="5">
         <v>33</v>
@@ -4747,16 +4747,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3030884685775703</v>
+        <v>-0.241581649889838</v>
       </c>
       <c r="O3" s="5">
         <v>83</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2501357122415683</v>
+        <v>0.2499015111943643</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1835975417850635</v>
+        <v>0.176668531369011</v>
       </c>
       <c r="R3" s="5">
         <v>83</v>
@@ -4806,16 +4806,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2897483402315749</v>
+        <v>-0.3097067167178409</v>
       </c>
       <c r="O4" s="5">
         <v>49</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1595933393258485</v>
+        <v>0.1571402635937763</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.10406034119885</v>
+        <v>0.1022344415093662</v>
       </c>
       <c r="R4" s="5">
         <v>48</v>
@@ -5062,13 +5062,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.3413113538540912</v>
+        <v>0.340476629529118</v>
       </c>
       <c r="I3" s="4">
-        <v>0.220082043142951</v>
+        <v>0.2188996847742853</v>
       </c>
       <c r="J3" s="4">
-        <v>0.2799742949122797</v>
+        <v>0.2824493590756758</v>
       </c>
       <c r="K3" s="4">
         <v>78.77165532879779</v>
@@ -5094,13 +5094,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>58.66666666666666</v>
+        <v>60.66666666666667</v>
       </c>
       <c r="C4" s="3">
         <v>12.66666666666667</v>
       </c>
       <c r="D4" s="3">
-        <v>28.66666666666667</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="E4" s="3">
         <v>4.666666666666667</v>
@@ -5109,16 +5109,16 @@
         <v>13.33333333333333</v>
       </c>
       <c r="G4" s="3">
-        <v>10.66666666666667</v>
+        <v>8.666666666666668</v>
       </c>
       <c r="H4" s="4">
-        <v>1.097649705016846</v>
+        <v>0.9825651615775727</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5556638578471638</v>
+        <v>0.4507867369163505</v>
       </c>
       <c r="J4" s="4">
-        <v>1.180437216081934</v>
+        <v>1.168135790885927</v>
       </c>
       <c r="K4" s="4">
         <v>81.90634920634926</v>
@@ -5162,13 +5162,13 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H5" s="4">
-        <v>0.3160247935454956</v>
+        <v>0.3157113107062516</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2048511129716927</v>
+        <v>0.2026207748746573</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2645581233348713</v>
+        <v>0.2592224219490502</v>
       </c>
       <c r="K5" s="4">
         <v>87.02789115646294</v>
@@ -5194,13 +5194,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>80</v>
+        <v>79.33333333333333</v>
       </c>
       <c r="C6" s="3">
         <v>7.333333333333333</v>
       </c>
       <c r="D6" s="3">
-        <v>12.66666666666667</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="E6" s="3">
         <v>0.6666666666666667</v>
@@ -5209,16 +5209,16 @@
         <v>12</v>
       </c>
       <c r="G6" s="3">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="H6" s="4">
-        <v>0.298168424783687</v>
+        <v>0.2956219300163747</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2332432099587303</v>
+        <v>0.215835196573554</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2774532374712938</v>
+        <v>0.2755038165859545</v>
       </c>
       <c r="K6" s="4">
         <v>85.31678004535165</v>
@@ -5262,13 +5262,13 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1927166858575508</v>
+        <v>0.1907897004805492</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1330460883324069</v>
+        <v>0.1308718279512636</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1604469317728042</v>
+        <v>0.1588079497922032</v>
       </c>
       <c r="K7" s="4">
         <v>90.42925170068015</v>
@@ -5312,13 +5312,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.3534307674664469</v>
+        <v>0.3537668157734049</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2539940492827608</v>
+        <v>0.251359415396658</v>
       </c>
       <c r="J8" s="4">
-        <v>0.2770661388025399</v>
+        <v>0.273572702999439</v>
       </c>
       <c r="K8" s="4">
         <v>86.4476190476192</v>
@@ -5362,13 +5362,13 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4187177583575126</v>
+        <v>0.4199924288858534</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3070870764012797</v>
+        <v>0.3064033876696292</v>
       </c>
       <c r="J9" s="4">
-        <v>0.3570810076594037</v>
+        <v>0.3584012856804219</v>
       </c>
       <c r="K9" s="4">
         <v>82.15873015873031</v>
@@ -5412,13 +5412,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.2809102929895312</v>
+        <v>0.282761955028217</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1724312814369397</v>
+        <v>0.1692767855429348</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1997015852861663</v>
+        <v>0.1930249449956472</v>
       </c>
       <c r="K10" s="4">
         <v>89.68072562358273</v>
@@ -5462,13 +5462,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.2908878337921823</v>
+        <v>0.2932504774000823</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1959179128550635</v>
+        <v>0.195300760435438</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2300751838357041</v>
+        <v>0.2266489306654139</v>
       </c>
       <c r="K11" s="4">
         <v>87.11269841269835</v>
@@ -5494,13 +5494,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>84</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="C12" s="3">
         <v>3.333333333333333</v>
       </c>
       <c r="D12" s="3">
-        <v>12.66666666666667</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="E12" s="3">
         <v>0.6666666666666667</v>
@@ -5509,16 +5509,16 @@
         <v>11.33333333333333</v>
       </c>
       <c r="G12" s="3">
-        <v>0.6666666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2339452016330015</v>
+        <v>0.2307178751241039</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1699596767771853</v>
+        <v>0.1491851163518342</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1766604369198356</v>
+        <v>0.16860578710921</v>
       </c>
       <c r="K12" s="4">
         <v>90.18163265306174</v>
@@ -5562,13 +5562,13 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H13" s="4">
-        <v>0.2654377671183818</v>
+        <v>0.2650117838678547</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1630613562406029</v>
+        <v>0.1623974838332227</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2209061411446297</v>
+        <v>0.2207967711110776</v>
       </c>
       <c r="K13" s="4">
         <v>86.13990929705218</v>
@@ -5612,13 +5612,13 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H14" s="4">
-        <v>0.7977067634844542</v>
+        <v>0.8013657190118036</v>
       </c>
       <c r="I14" s="4">
-        <v>0.25470324579278</v>
+        <v>0.2466761007090815</v>
       </c>
       <c r="J14" s="4">
-        <v>0.5206484418501753</v>
+        <v>0.5161401679960825</v>
       </c>
       <c r="K14" s="4">
         <v>65.64920634920631</v>
@@ -5662,13 +5662,13 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2296059952696585</v>
+        <v>0.2244756585453205</v>
       </c>
       <c r="I15" s="4">
-        <v>0.146714608002139</v>
+        <v>0.1398306522478177</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1920989003266503</v>
+        <v>0.1850247751726997</v>
       </c>
       <c r="K15" s="4">
         <v>93.73038548752803</v>
@@ -5712,13 +5712,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.9315447248715587</v>
+        <v>0.9448984686101518</v>
       </c>
       <c r="I16" s="4">
-        <v>0.3169140037796576</v>
+        <v>0.3105205497366346</v>
       </c>
       <c r="J16" s="4">
-        <v>0.5613040708695983</v>
+        <v>0.5605831564347591</v>
       </c>
       <c r="K16" s="4">
         <v>57.39433106575969</v>
@@ -5762,13 +5762,13 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2462054229173934</v>
+        <v>0.2452113800213233</v>
       </c>
       <c r="I17" s="4">
-        <v>0.165502989891609</v>
+        <v>0.1605570865361792</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1978076080321659</v>
+        <v>0.1936043696887846</v>
       </c>
       <c r="K17" s="4">
         <v>91.56485260770958</v>
@@ -6695,13 +6695,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C4" s="5">
         <v>19</v>
       </c>
       <c r="D4" s="5">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E4" s="5">
         <v>7</v>
@@ -6710,7 +6710,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H4" s="5">
         <v>7</v>
@@ -6783,13 +6783,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C6" s="5">
         <v>11</v>
       </c>
       <c r="D6" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" s="5">
         <v>1</v>
@@ -6798,7 +6798,7 @@
         <v>18</v>
       </c>
       <c r="G6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="5">
         <v>1</v>
@@ -7047,13 +7047,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" s="5">
         <v>5</v>
       </c>
       <c r="D12" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" s="5">
         <v>1</v>
@@ -7062,7 +7062,7 @@
         <v>17</v>
       </c>
       <c r="G12" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="5">
         <v>1</v>
@@ -7465,16 +7465,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1103552779539539</v>
+        <v>0.1072704321802007</v>
       </c>
       <c r="O3" s="5">
         <v>57</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3942957001519485</v>
+        <v>0.3934909577761867</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2186790235554268</v>
+        <v>0.2186249034541329</v>
       </c>
       <c r="R3" s="5">
         <v>57</v>
@@ -7524,16 +7524,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.07532231913081976</v>
+        <v>-0.1250456991144233</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2392062686247563</v>
+        <v>0.2382221849675275</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2190482514754993</v>
+        <v>0.2163842420406663</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -7816,22 +7816,22 @@
         <v>11</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7998774803440117</v>
+        <v>0.2449890921874953</v>
       </c>
       <c r="O3" s="5">
         <v>58</v>
       </c>
       <c r="P3" s="4">
-        <v>1.472401488161479</v>
+        <v>1.285335403641875</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7764264586803147</v>
+        <v>0.5598215979003092</v>
       </c>
       <c r="R3" s="5">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="S3" s="5">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7875,16 +7875,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.07862271773621998</v>
+        <v>-0.09208491250824835</v>
       </c>
       <c r="O4" s="5">
         <v>44</v>
       </c>
       <c r="P4" s="4">
-        <v>0.342465699162893</v>
+        <v>0.3414541272381382</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3349012570140129</v>
+        <v>0.3343176808653038</v>
       </c>
       <c r="R4" s="5">
         <v>44</v>
@@ -8163,16 +8163,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1260380636559079</v>
+        <v>-0.09235415801705926</v>
       </c>
       <c r="O3" s="5">
         <v>77</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3033658310823035</v>
+        <v>0.3028478622501296</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1966136723226317</v>
+        <v>0.1929326272313077</v>
       </c>
       <c r="R3" s="5">
         <v>77</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1377858294664694</v>
+        <v>-0.1331035667899272</v>
       </c>
       <c r="O4" s="5">
         <v>50</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2442973644435555</v>
+        <v>0.2443094934180439</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1773784970365255</v>
+        <v>0.1772038206629318</v>
       </c>
       <c r="R4" s="5">
         <v>50</v>
@@ -8518,16 +8518,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.009215761610058758</v>
+        <v>0.01990819912720099</v>
       </c>
       <c r="O3" s="5">
         <v>73</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3062863008408607</v>
+        <v>0.3072235151154491</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2354575839626198</v>
+        <v>0.2350275415047234</v>
       </c>
       <c r="R3" s="5">
         <v>73</v>
@@ -8577,22 +8577,22 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.05657985342837273</v>
+        <v>-0.11237100960021</v>
       </c>
       <c r="O4" s="5">
         <v>44</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2505196885083327</v>
+        <v>0.2415158821937368</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2258125623983473</v>
+        <v>0.1781941637711397</v>
       </c>
       <c r="R4" s="5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -8873,16 +8873,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02695554500291967</v>
+        <v>-0.01309686178464631</v>
       </c>
       <c r="O3" s="5">
         <v>82</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1733151506807306</v>
+        <v>0.1727143848088005</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1375770171275927</v>
+        <v>0.1362269537972187</v>
       </c>
       <c r="R3" s="5">
         <v>82</v>
@@ -8932,16 +8932,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03501395579928168</v>
+        <v>-0.05344925870970485</v>
       </c>
       <c r="O4" s="5">
         <v>48</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1604445239545811</v>
+        <v>0.1559488057558758</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09251338060409535</v>
+        <v>0.08871611597427825</v>
       </c>
       <c r="R4" s="5">
         <v>47</v>
